--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N84_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N84_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.97560175934752</v>
+        <v>6.333535285893972</v>
       </c>
       <c r="D2" t="n">
-        <v>37.26049555364612</v>
+        <v>6.054830527467495</v>
       </c>
       <c r="E2" t="n">
-        <v>12.20629273534951</v>
+        <v>1.983522569494296</v>
       </c>
       <c r="F2" t="n">
-        <v>12.62406809990084</v>
+        <v>2.051411066233887</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>28.5196168292369</v>
+        <v>4.634437734750997</v>
       </c>
       <c r="D3" t="n">
-        <v>27.94602596879055</v>
+        <v>4.541229219928465</v>
       </c>
       <c r="E3" t="n">
-        <v>12.20629273534951</v>
+        <v>1.983522569494296</v>
       </c>
       <c r="F3" t="n">
-        <v>12.62406809990084</v>
+        <v>2.051411066233887</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.4149334168534</v>
+        <v>2.179926680238677</v>
       </c>
       <c r="D4" t="n">
-        <v>8.455243716845054</v>
+        <v>1.373977103987321</v>
       </c>
       <c r="E4" t="n">
-        <v>12.20629273534951</v>
+        <v>1.983522569494296</v>
       </c>
       <c r="F4" t="n">
-        <v>12.62406809990084</v>
+        <v>2.051411066233887</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.87400313325663</v>
+        <v>5.829525509154203</v>
       </c>
       <c r="D5" t="n">
-        <v>36.29062454272334</v>
+        <v>5.897226488192542</v>
       </c>
       <c r="E5" t="n">
-        <v>12.20629273534951</v>
+        <v>1.983522569494296</v>
       </c>
       <c r="F5" t="n">
-        <v>12.62406809990084</v>
+        <v>2.051411066233887</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>9.405575612779359</v>
+        <v>1.528406037076646</v>
       </c>
       <c r="D6" t="n">
-        <v>9.356674836669269</v>
+        <v>1.520459660958756</v>
       </c>
       <c r="E6" t="n">
-        <v>12.20629273534951</v>
+        <v>1.983522569494296</v>
       </c>
       <c r="F6" t="n">
-        <v>12.62406809990084</v>
+        <v>2.051411066233887</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10.10272940690338</v>
+        <v>1.641693528621799</v>
       </c>
       <c r="D7" t="n">
-        <v>10.10272940690338</v>
+        <v>1.641693528621799</v>
       </c>
       <c r="E7" t="n">
-        <v>12.20629273534951</v>
+        <v>1.983522569494296</v>
       </c>
       <c r="F7" t="n">
-        <v>12.62406809990084</v>
+        <v>2.051411066233887</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
